--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:07</t>
+    <t xml:space="preserve">2026-09-09 23:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:00</t>
+    <t xml:space="preserve">2026-09-17 13:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:57</t>
+    <t xml:space="preserve">2026-09-23 12:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:26</t>
+    <t xml:space="preserve">2026-10-02 13:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:16</t>
+    <t xml:space="preserve">2026-10-04 08:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:47</t>
+    <t xml:space="preserve">2026-10-05 09:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -813,7 +813,7 @@
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>711841.12</v>
+        <v>711841.13</v>
       </c>
     </row>
     <row r="16">
@@ -1068,7 +1068,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>627794.12</v>
+        <v>627794.13</v>
       </c>
     </row>
     <row r="31">
@@ -1085,7 +1085,7 @@
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>616548.12</v>
+        <v>616548.13</v>
       </c>
     </row>
     <row r="32">
@@ -1119,7 +1119,7 @@
         <v>2018</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>601534.62</v>
+        <v>601534.63</v>
       </c>
     </row>
     <row r="34">
@@ -1136,7 +1136,7 @@
         <v>2018</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>600274.62</v>
+        <v>600274.63</v>
       </c>
     </row>
     <row r="35">
@@ -1153,7 +1153,7 @@
         <v>2018</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>592647.12</v>
+        <v>592647.13</v>
       </c>
     </row>
     <row r="36">
